--- a/artfynd/A 3853-2025 artfynd.xlsx
+++ b/artfynd/A 3853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69510844</v>
+        <v>88767309</v>
       </c>
       <c r="B2" t="n">
-        <v>85077</v>
+        <v>96355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3762</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandbysjön 5,5 km NV om Västlands kyrka, Upl</t>
+          <t>Fd Sandbysjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640750.215145671</v>
+        <v>640746.8246305889</v>
       </c>
       <c r="R2" t="n">
-        <v>6708818.015307377</v>
+        <v>6709031.971705756</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-09-28</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -764,17 +764,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-09-28</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca. 5 ex. i medelåldrig barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,30 +781,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Medelåldrig, örtrik barrskog.</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88767309</v>
+        <v>98361522</v>
       </c>
       <c r="B3" t="n">
-        <v>96355</v>
+        <v>96312</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,43 +812,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fd Sandbysjön, Upl</t>
+          <t>Dängnäs, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>640746.8246305889</v>
+        <v>640742.3846141072</v>
       </c>
       <c r="R3" t="n">
-        <v>6709031.971705756</v>
+        <v>6709031.798808919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +870,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -895,7 +880,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -915,19 +900,23 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98361520</v>
+        <v>98361482</v>
       </c>
       <c r="B4" t="n">
         <v>96356</v>
@@ -962,7 +951,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -971,13 +960,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640733.5295384605</v>
+        <v>640739.4384696844</v>
       </c>
       <c r="R4" t="n">
-        <v>6708878.535016823</v>
+        <v>6709044.015984816</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1044,612 +1033,6 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>98361522</v>
-      </c>
-      <c r="B5" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>219798</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Epipactis helleborine</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Dängnäs, Upl</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>640742.3846141072</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6709031.798808919</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Tierp</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Västland</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2021-07-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2021-07-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>98361482</v>
-      </c>
-      <c r="B6" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>219847</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Dängnäs, Upl</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>640739.4384696844</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6709044.015984816</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Tierp</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Västland</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2021-07-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2021-07-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>98361521</v>
-      </c>
-      <c r="B7" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>222002</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Underviol</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Viola mirabilis</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Dängnäs, Upl</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>640731.4218726414</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6708881.906034915</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Tierp</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Västland</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2021-07-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2021-07-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>98361519</v>
-      </c>
-      <c r="B8" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>504</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Guckusko</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Cypripedium calceolus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Dängnäs, Upl</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>640754.3847554957</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6708875.893997493</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Tierp</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Västland</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2021-07-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2021-07-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>88767717</v>
-      </c>
-      <c r="B9" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>504</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Guckusko</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Cypripedium calceolus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Fd Sandbysjön, Upl</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>640762.9083479012</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6708821.962731223</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Tierp</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Västland</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2020-06-10</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2020-06-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>inom 20m, tre grupper</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3853-2025 artfynd.xlsx
+++ b/artfynd/A 3853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88767309</v>
+        <v>69510844</v>
       </c>
       <c r="B2" t="n">
-        <v>96355</v>
+        <v>85077</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fd Sandbysjön, Upl</t>
+          <t>Sandbysjön 5,5 km NV om Västlands kyrka, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640746.8246305889</v>
+        <v>640750.215145671</v>
       </c>
       <c r="R2" t="n">
-        <v>6709031.971705756</v>
+        <v>6708818.015307377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2005-09-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2005-09-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -772,6 +772,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. i medelåldrig barrskog.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,26 +785,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Medelåldrig, örtrik barrskog.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98361522</v>
+        <v>88767309</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
+        <v>96355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,38 +822,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dängnäs, Upl</t>
+          <t>Fd Sandbysjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>640742.3846141072</v>
+        <v>640746.8246305889</v>
       </c>
       <c r="R3" t="n">
-        <v>6709031.798808919</v>
+        <v>6709031.971705756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +885,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -880,7 +895,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -900,23 +915,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98361482</v>
+        <v>98361520</v>
       </c>
       <c r="B4" t="n">
         <v>96356</v>
@@ -951,7 +962,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -960,13 +971,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640739.4384696844</v>
+        <v>640733.5295384605</v>
       </c>
       <c r="R4" t="n">
-        <v>6709044.015984816</v>
+        <v>6708878.535016823</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1033,6 +1044,612 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98361522</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96312</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dängnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>640742.3846141072</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6709031.798808919</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>98361482</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96356</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dängnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>640739.4384696844</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6709044.015984816</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>98361521</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101120</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dängnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>640731.4218726414</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6708881.906034915</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>98361519</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96239</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>504</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dängnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>640754.3847554957</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6708875.893997493</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>88767717</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96239</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>504</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fd Sandbysjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>640762.9083479012</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6708821.962731223</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-06-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-06-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>inom 20m, tre grupper</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3853-2025 artfynd.xlsx
+++ b/artfynd/A 3853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98361482</v>
+        <v>88767572</v>
       </c>
       <c r="B2" t="n">
-        <v>96356</v>
+        <v>95511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +713,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dängnäs, Upl</t>
+          <t>Fd Sandbysjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640739.4384696844</v>
+        <v>640746.7809328033</v>
       </c>
       <c r="R2" t="n">
-        <v>6709044.015984816</v>
+        <v>6709045.781727909</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,7 +754,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2020-04-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2020-04-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -779,15 +784,131 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>98361482</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96356</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dängnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>640739.4384696844</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6709044.015984816</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Charles Campbell</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
